--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -10010,7 +10010,7 @@
     <t>Fix_Resource/스킬 이펙트/A2. 허리케인/sheet.png</t>
   </si>
   <si>
-    <t>스킬 이펙트 · 허리케인 (시트 4×3, 프레임 540×540px. 낱장은 frames 폴더)</t>
+    <t>스킬 이펙트 · 허리케인 (시트 3×6, 프레임 400×340px. 낱장은 frames 폴더)</t>
   </si>
   <si>
     <t>res8000003</t>
@@ -41928,7 +41928,7 @@
       </c>
       <c r="F318" s="5"/>
       <c r="G318" s="5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H318" s="5">
         <v>12</v>

--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -30442,7 +30442,7 @@
         <v>7</v>
       </c>
       <c r="M26" s="51">
-        <v>-0.6</v>
+        <v>-0.35</v>
       </c>
       <c r="N26" s="51">
         <v>1</v>
@@ -41998,24 +41998,30 @@
       <c r="B321" s="5">
         <v>80</v>
       </c>
-      <c r="C321" s="4" t="s">
-        <v>3158</v>
-      </c>
-      <c r="D321" s="4" t="s">
-        <v>3171</v>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>frame_00.png</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>Fix_Resource/스킬 이펙트/P2. 파이어브레스/frame_00.png</t>
+        </is>
       </c>
       <c r="E321" s="5">
         <v>0</v>
       </c>
       <c r="F321" s="5"/>
       <c r="G321" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H321" s="5">
         <v>12</v>
       </c>
-      <c r="I321" s="4" t="s">
-        <v>3172</v>
+      <c r="I321" s="4" t="inlineStr">
+        <is>
+          <t>스킬 이펙트 · 파이어브레스 Ver02 (낱장 11장, 프레임 540×540px, 왼쪽 끝이 입. 0~2 커짐, 3~6 유지, 7~10 사그라듦)</t>
+        </is>
       </c>
     </row>
     <row r="322" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -42025,11 +42031,15 @@
       <c r="B322" s="5">
         <v>80</v>
       </c>
-      <c r="C322" s="4" t="s">
-        <v>3158</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>3174</v>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>frame_00.png</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>Fix_Resource/스킬 이펙트/P3. 번개(낙뢰)_골드/frame_00.png</t>
+        </is>
       </c>
       <c r="E322" s="5">
         <v>0</v>
@@ -42041,8 +42051,10 @@
       <c r="H322" s="5">
         <v>12</v>
       </c>
-      <c r="I322" s="4" t="s">
-        <v>3175</v>
+      <c r="I322" s="4" t="inlineStr">
+        <is>
+          <t>스킬 이펙트 · 번개(낙뢰)_골드 Ver02 (낱장, 프레임 256×512px, 12장)</t>
+        </is>
       </c>
     </row>
     <row r="323" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -42052,11 +42064,15 @@
       <c r="B323" s="5">
         <v>80</v>
       </c>
-      <c r="C323" s="4" t="s">
-        <v>3158</v>
-      </c>
-      <c r="D323" s="4" t="s">
-        <v>3177</v>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>frame_00.png</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr">
+        <is>
+          <t>Fix_Resource/스킬 이펙트/P3. 번개(낙뢰)_블루/frame_00.png</t>
+        </is>
       </c>
       <c r="E323" s="5">
         <v>0</v>
@@ -42068,8 +42084,10 @@
       <c r="H323" s="5">
         <v>12</v>
       </c>
-      <c r="I323" s="4" t="s">
-        <v>3178</v>
+      <c r="I323" s="4" t="inlineStr">
+        <is>
+          <t>스킬 이펙트 · 번개(낙뢰)_블루 Ver02 (낱장, 프레임 256×512px, 12장)</t>
+        </is>
       </c>
     </row>
     <row r="324" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -42079,11 +42097,15 @@
       <c r="B324" s="5">
         <v>80</v>
       </c>
-      <c r="C324" s="4" t="s">
-        <v>3158</v>
-      </c>
-      <c r="D324" s="4" t="s">
-        <v>3180</v>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>frame_00.png</t>
+        </is>
+      </c>
+      <c r="D324" s="4" t="inlineStr">
+        <is>
+          <t>Fix_Resource/스킬 이펙트/P3. 번개(연쇄)_골드/frame_00.png</t>
+        </is>
       </c>
       <c r="E324" s="5">
         <v>0</v>
@@ -42095,8 +42117,10 @@
       <c r="H324" s="5">
         <v>12</v>
       </c>
-      <c r="I324" s="4" t="s">
-        <v>3181</v>
+      <c r="I324" s="4" t="inlineStr">
+        <is>
+          <t>스킬 이펙트 · 번개(연쇄)_골드 Ver02 (낱장, 프레임 540×540px, 6장)</t>
+        </is>
       </c>
     </row>
     <row r="325" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -42106,11 +42130,15 @@
       <c r="B325" s="5">
         <v>80</v>
       </c>
-      <c r="C325" s="4" t="s">
-        <v>3158</v>
-      </c>
-      <c r="D325" s="4" t="s">
-        <v>3183</v>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>frame_00.png</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>Fix_Resource/스킬 이펙트/P3. 번개(연쇄)_블루/frame_00.png</t>
+        </is>
       </c>
       <c r="E325" s="5">
         <v>0</v>
@@ -42122,8 +42150,10 @@
       <c r="H325" s="5">
         <v>12</v>
       </c>
-      <c r="I325" s="4" t="s">
-        <v>3184</v>
+      <c r="I325" s="4" t="inlineStr">
+        <is>
+          <t>스킬 이펙트 · 번개(연쇄)_블루 Ver02 (낱장, 프레임 540×540px, 6장)</t>
+        </is>
       </c>
     </row>
     <row r="326" spans="1:9" ht="27" x14ac:dyDescent="0.3">

--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -18098,10 +18098,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="5">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="F5" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -18170,7 +18170,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="5">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -18206,10 +18206,10 @@
         <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="F8" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -18242,10 +18242,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="5">
-        <v>1105</v>
+        <v>216</v>
       </c>
       <c r="F9" s="5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
@@ -18276,7 +18276,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="5">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -18348,10 +18348,10 @@
         <v>2</v>
       </c>
       <c r="E12" s="5">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F12" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G12" s="5">
         <v>1</v>
@@ -18456,10 +18456,10 @@
         <v>3</v>
       </c>
       <c r="E15" s="5">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="F15" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G15" s="5">
         <v>1</v>
@@ -18492,10 +18492,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="5">
-        <v>1235</v>
+        <v>370</v>
       </c>
       <c r="F16" s="5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
@@ -18598,10 +18598,10 @@
         <v>3</v>
       </c>
       <c r="E19" s="5">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="F19" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G19" s="5">
         <v>1</v>
@@ -18670,7 +18670,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="5">
-        <v>480</v>
+        <v>216</v>
       </c>
       <c r="F21" s="5">
         <v>0</v>
@@ -18706,10 +18706,10 @@
         <v>5</v>
       </c>
       <c r="E22" s="5">
-        <v>811</v>
+        <v>178</v>
       </c>
       <c r="F22" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G22" s="5">
         <v>1</v>
@@ -18742,10 +18742,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="5">
-        <v>3120</v>
+        <v>515</v>
       </c>
       <c r="F23" s="5">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5">
         <v>1</v>
@@ -18776,7 +18776,7 @@
         <v>13</v>
       </c>
       <c r="E24" s="5">
-        <v>720</v>
+        <v>324</v>
       </c>
       <c r="F24" s="5">
         <v>0</v>
@@ -18848,10 +18848,10 @@
         <v>4</v>
       </c>
       <c r="E26" s="5">
-        <v>460</v>
+        <v>184</v>
       </c>
       <c r="F26" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G26" s="5">
         <v>1</v>
@@ -18956,10 +18956,10 @@
         <v>5</v>
       </c>
       <c r="E29" s="5">
-        <v>748</v>
+        <v>299</v>
       </c>
       <c r="F29" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G29" s="5">
         <v>1</v>
@@ -18992,10 +18992,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="5">
-        <v>2860</v>
+        <v>858</v>
       </c>
       <c r="F30" s="5">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5">
         <v>1</v>
@@ -19098,10 +19098,10 @@
         <v>5</v>
       </c>
       <c r="E33" s="5">
-        <v>667</v>
+        <v>267</v>
       </c>
       <c r="F33" s="5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G33" s="5">
         <v>1</v>
@@ -19170,7 +19170,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="5">
-        <v>6300</v>
+        <v>3780</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
@@ -19206,10 +19206,10 @@
         <v>7</v>
       </c>
       <c r="E36" s="5">
-        <v>10647</v>
+        <v>2130</v>
       </c>
       <c r="F36" s="5">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G36" s="5">
         <v>1</v>
@@ -19242,10 +19242,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="5">
-        <v>40950</v>
+        <v>6757</v>
       </c>
       <c r="F37" s="5">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5">
         <v>1</v>
@@ -19276,7 +19276,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="5">
-        <v>2100</v>
+        <v>1260</v>
       </c>
       <c r="F38" s="5">
         <v>0</v>
@@ -19348,10 +19348,10 @@
         <v>6</v>
       </c>
       <c r="E40" s="5">
-        <v>1050</v>
+        <v>420</v>
       </c>
       <c r="F40" s="5">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G40" s="5">
         <v>1</v>
@@ -19456,10 +19456,10 @@
         <v>7</v>
       </c>
       <c r="E43" s="5">
-        <v>1690</v>
+        <v>676</v>
       </c>
       <c r="F43" s="5">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G43" s="5">
         <v>1</v>
@@ -19492,10 +19492,10 @@
         <v>1</v>
       </c>
       <c r="E44" s="5">
-        <v>6500</v>
+        <v>1950</v>
       </c>
       <c r="F44" s="5">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="G44" s="5">
         <v>1</v>
@@ -19598,10 +19598,10 @@
         <v>7</v>
       </c>
       <c r="E47" s="5">
-        <v>1872</v>
+        <v>749</v>
       </c>
       <c r="F47" s="5">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G47" s="5">
         <v>1</v>
@@ -19706,10 +19706,10 @@
         <v>9</v>
       </c>
       <c r="E50" s="5">
-        <v>16562</v>
+        <v>6625</v>
       </c>
       <c r="F50" s="5">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="G50" s="5">
         <v>1</v>
@@ -19742,10 +19742,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>63700</v>
+        <v>57330</v>
       </c>
       <c r="F51" s="5">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="G51" s="5">
         <v>1</v>
@@ -19848,10 +19848,10 @@
         <v>8</v>
       </c>
       <c r="E54" s="5">
-        <v>2340</v>
+        <v>936</v>
       </c>
       <c r="F54" s="5">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="G54" s="5">
         <v>1</v>
@@ -19956,10 +19956,10 @@
         <v>9</v>
       </c>
       <c r="E57" s="5">
-        <v>3803</v>
+        <v>1521</v>
       </c>
       <c r="F57" s="5">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="G57" s="5">
         <v>1</v>
@@ -19992,10 +19992,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="5">
-        <v>14625</v>
+        <v>4388</v>
       </c>
       <c r="F58" s="5">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="G58" s="5">
         <v>1</v>
@@ -20098,10 +20098,10 @@
         <v>9</v>
       </c>
       <c r="E61" s="5">
-        <v>14040</v>
+        <v>5616</v>
       </c>
       <c r="F61" s="5">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="G61" s="5">
         <v>1</v>
@@ -20206,10 +20206,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="5">
-        <v>359632</v>
+        <v>143853</v>
       </c>
       <c r="F64" s="5">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="G64" s="5">
         <v>1</v>
@@ -20242,10 +20242,10 @@
         <v>1</v>
       </c>
       <c r="E65" s="5">
-        <v>1383200</v>
+        <v>414960</v>
       </c>
       <c r="F65" s="5">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="G65" s="5">
         <v>1</v>
@@ -20348,10 +20348,10 @@
         <v>10</v>
       </c>
       <c r="E68" s="5">
-        <v>5330</v>
+        <v>2132</v>
       </c>
       <c r="F68" s="5">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="G68" s="5">
         <v>1</v>
@@ -20456,10 +20456,10 @@
         <v>11</v>
       </c>
       <c r="E71" s="5">
-        <v>8619</v>
+        <v>3448</v>
       </c>
       <c r="F71" s="5">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="G71" s="5">
         <v>1</v>
@@ -20492,10 +20492,10 @@
         <v>1</v>
       </c>
       <c r="E72" s="5">
-        <v>33150</v>
+        <v>9945</v>
       </c>
       <c r="F72" s="5">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="G72" s="5">
         <v>1</v>
@@ -20598,10 +20598,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="5">
-        <v>39780</v>
+        <v>15912</v>
       </c>
       <c r="F75" s="5">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="G75" s="5">
         <v>1</v>
@@ -20706,10 +20706,10 @@
         <v>13</v>
       </c>
       <c r="E78" s="5">
-        <v>338000</v>
+        <v>135200</v>
       </c>
       <c r="F78" s="5">
-        <v>285</v>
+        <v>384</v>
       </c>
       <c r="G78" s="5">
         <v>1</v>
@@ -20742,10 +20742,10 @@
         <v>1</v>
       </c>
       <c r="E79" s="5">
-        <v>1300000</v>
+        <v>1170000</v>
       </c>
       <c r="F79" s="5">
-        <v>450</v>
+        <v>180</v>
       </c>
       <c r="G79" s="5">
         <v>1</v>
@@ -20848,10 +20848,10 @@
         <v>12</v>
       </c>
       <c r="E82" s="5">
-        <v>12090</v>
+        <v>4836</v>
       </c>
       <c r="F82" s="5">
-        <v>238</v>
+        <v>107</v>
       </c>
       <c r="G82" s="5">
         <v>1</v>
@@ -20956,10 +20956,10 @@
         <v>13</v>
       </c>
       <c r="E85" s="5">
-        <v>19604</v>
+        <v>7842</v>
       </c>
       <c r="F85" s="5">
-        <v>285</v>
+        <v>128</v>
       </c>
       <c r="G85" s="5">
         <v>1</v>
@@ -20992,10 +20992,10 @@
         <v>1</v>
       </c>
       <c r="E86" s="5">
-        <v>75400</v>
+        <v>22620</v>
       </c>
       <c r="F86" s="5">
-        <v>450</v>
+        <v>36</v>
       </c>
       <c r="G86" s="5">
         <v>1</v>
@@ -21098,10 +21098,10 @@
         <v>13</v>
       </c>
       <c r="E89" s="5">
-        <v>292500</v>
+        <v>117000</v>
       </c>
       <c r="F89" s="5">
-        <v>340</v>
+        <v>153</v>
       </c>
       <c r="G89" s="5">
         <v>1</v>
@@ -21206,10 +21206,10 @@
         <v>15</v>
       </c>
       <c r="E92" s="5">
-        <v>1605500</v>
+        <v>642200</v>
       </c>
       <c r="F92" s="5">
-        <v>590</v>
+        <v>399</v>
       </c>
       <c r="G92" s="5">
         <v>1</v>
@@ -21242,10 +21242,10 @@
         <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>6175000</v>
+        <v>2778750</v>
       </c>
       <c r="F93" s="5">
-        <v>940</v>
+        <v>150</v>
       </c>
       <c r="G93" s="5">
         <v>1</v>
@@ -21348,10 +21348,10 @@
         <v>14</v>
       </c>
       <c r="E96" s="5">
-        <v>27300</v>
+        <v>10920</v>
       </c>
       <c r="F96" s="5">
-        <v>490</v>
+        <v>220</v>
       </c>
       <c r="G96" s="5">
         <v>1</v>
@@ -21456,10 +21456,10 @@
         <v>15</v>
       </c>
       <c r="E99" s="5">
-        <v>43940</v>
+        <v>17576</v>
       </c>
       <c r="F99" s="5">
-        <v>590</v>
+        <v>266</v>
       </c>
       <c r="G99" s="5">
         <v>1</v>
@@ -21492,10 +21492,10 @@
         <v>1</v>
       </c>
       <c r="E100" s="5">
-        <v>169000</v>
+        <v>50700</v>
       </c>
       <c r="F100" s="5">
-        <v>940</v>
+        <v>75</v>
       </c>
       <c r="G100" s="5">
         <v>1</v>
@@ -21695,7 +21695,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5">
         <v>0.5</v>
@@ -21730,7 +21730,7 @@
         <v>60</v>
       </c>
       <c r="G5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
         <v>0.5</v>
@@ -21765,7 +21765,7 @@
         <v>60</v>
       </c>
       <c r="G6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5">
         <v>0.5</v>
@@ -21800,7 +21800,7 @@
         <v>102</v>
       </c>
       <c r="G7" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" s="5">
         <v>0.5</v>
@@ -21835,7 +21835,7 @@
         <v>102</v>
       </c>
       <c r="G8" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H8" s="5">
         <v>0.5</v>
@@ -21870,7 +21870,7 @@
         <v>177</v>
       </c>
       <c r="G9" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H9" s="5">
         <v>0.5</v>
@@ -21905,7 +21905,7 @@
         <v>90</v>
       </c>
       <c r="G10" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5">
         <v>0.5</v>
@@ -21940,7 +21940,7 @@
         <v>90</v>
       </c>
       <c r="G11" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="5">
         <v>0.5</v>
@@ -21975,7 +21975,7 @@
         <v>90</v>
       </c>
       <c r="G12" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5">
         <v>0.5</v>
@@ -22010,7 +22010,7 @@
         <v>114</v>
       </c>
       <c r="G13" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H13" s="5">
         <v>0.5</v>
@@ -22045,7 +22045,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5">
         <v>0.5</v>
@@ -22080,7 +22080,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H15" s="5">
         <v>0.5</v>
@@ -22115,7 +22115,7 @@
         <v>120</v>
       </c>
       <c r="G16" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16" s="5">
         <v>0.5</v>
@@ -22150,7 +22150,7 @@
         <v>120</v>
       </c>
       <c r="G17" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" s="5">
         <v>0.5</v>
@@ -22185,7 +22185,7 @@
         <v>120</v>
       </c>
       <c r="G18" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" s="5">
         <v>0.5</v>
@@ -22220,7 +22220,7 @@
         <v>288</v>
       </c>
       <c r="G19" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H19" s="5">
         <v>0.5</v>
@@ -22255,7 +22255,7 @@
         <v>288</v>
       </c>
       <c r="G20" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H20" s="5">
         <v>0.5</v>
@@ -22290,7 +22290,7 @@
         <v>499</v>
       </c>
       <c r="G21" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H21" s="5">
         <v>0.5</v>
@@ -22325,7 +22325,7 @@
         <v>210</v>
       </c>
       <c r="G22" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H22" s="5">
         <v>0.5</v>
@@ -22360,7 +22360,7 @@
         <v>210</v>
       </c>
       <c r="G23" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H23" s="5">
         <v>0.5</v>
@@ -22395,7 +22395,7 @@
         <v>210</v>
       </c>
       <c r="G24" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H24" s="5">
         <v>0.5</v>
@@ -22430,7 +22430,7 @@
         <v>264</v>
       </c>
       <c r="G25" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H25" s="5">
         <v>0.5</v>
@@ -22465,7 +22465,7 @@
         <v>264</v>
       </c>
       <c r="G26" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H26" s="5">
         <v>0.5</v>
@@ -22500,7 +22500,7 @@
         <v>460</v>
       </c>
       <c r="G27" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H27" s="5">
         <v>0.5</v>
@@ -22535,7 +22535,7 @@
         <v>342</v>
       </c>
       <c r="G28" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H28" s="5">
         <v>0.5</v>
@@ -22570,7 +22570,7 @@
         <v>342</v>
       </c>
       <c r="G29" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H29" s="5">
         <v>0.5</v>
@@ -22605,7 +22605,7 @@
         <v>342</v>
       </c>
       <c r="G30" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H30" s="5">
         <v>0.5</v>
@@ -22640,7 +22640,7 @@
         <v>840</v>
       </c>
       <c r="G31" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H31" s="5">
         <v>0.5</v>
@@ -22675,7 +22675,7 @@
         <v>840</v>
       </c>
       <c r="G32" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H32" s="5">
         <v>0.5</v>
@@ -22710,7 +22710,7 @@
         <v>1456</v>
       </c>
       <c r="G33" s="5">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="H33" s="5">
         <v>0.5</v>
@@ -22745,7 +22745,7 @@
         <v>480</v>
       </c>
       <c r="G34" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H34" s="5">
         <v>0.5</v>
@@ -22780,7 +22780,7 @@
         <v>480</v>
       </c>
       <c r="G35" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H35" s="5">
         <v>0.5</v>
@@ -22815,7 +22815,7 @@
         <v>480</v>
       </c>
       <c r="G36" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H36" s="5">
         <v>0.5</v>
@@ -22850,7 +22850,7 @@
         <v>600</v>
       </c>
       <c r="G37" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H37" s="5">
         <v>0.5</v>
@@ -22885,7 +22885,7 @@
         <v>600</v>
       </c>
       <c r="G38" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H38" s="5">
         <v>0.5</v>
@@ -22920,7 +22920,7 @@
         <v>1040</v>
       </c>
       <c r="G39" s="5">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H39" s="5">
         <v>0.5</v>
@@ -22955,7 +22955,7 @@
         <v>960</v>
       </c>
       <c r="G40" s="5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H40" s="5">
         <v>0.5</v>
@@ -22990,7 +22990,7 @@
         <v>960</v>
       </c>
       <c r="G41" s="5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H41" s="5">
         <v>0.5</v>
@@ -23025,7 +23025,7 @@
         <v>960</v>
       </c>
       <c r="G42" s="5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H42" s="5">
         <v>0.5</v>
@@ -23060,7 +23060,7 @@
         <v>5880</v>
       </c>
       <c r="G43" s="5">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H43" s="5">
         <v>0.5</v>
@@ -23095,7 +23095,7 @@
         <v>5880</v>
       </c>
       <c r="G44" s="5">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H44" s="5">
         <v>0.5</v>
@@ -23130,7 +23130,7 @@
         <v>10192</v>
       </c>
       <c r="G45" s="5">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="H45" s="5">
         <v>0.5</v>
@@ -23165,7 +23165,7 @@
         <v>1080</v>
       </c>
       <c r="G46" s="5">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H46" s="5">
         <v>0.5</v>
@@ -23200,7 +23200,7 @@
         <v>1080</v>
       </c>
       <c r="G47" s="5">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H47" s="5">
         <v>0.5</v>
@@ -23235,7 +23235,7 @@
         <v>1080</v>
       </c>
       <c r="G48" s="5">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H48" s="5">
         <v>0.5</v>
@@ -23270,7 +23270,7 @@
         <v>1350</v>
       </c>
       <c r="G49" s="5">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H49" s="5">
         <v>0.5</v>
@@ -23305,7 +23305,7 @@
         <v>1350</v>
       </c>
       <c r="G50" s="5">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H50" s="5">
         <v>0.5</v>
@@ -23340,7 +23340,7 @@
         <v>2340</v>
       </c>
       <c r="G51" s="5">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="H51" s="5">
         <v>0.5</v>
@@ -23375,7 +23375,7 @@
         <v>7200</v>
       </c>
       <c r="G52" s="5">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H52" s="5">
         <v>0.5</v>
@@ -23410,7 +23410,7 @@
         <v>7200</v>
       </c>
       <c r="G53" s="5">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H53" s="5">
         <v>0.5</v>
@@ -23445,7 +23445,7 @@
         <v>7200</v>
       </c>
       <c r="G54" s="5">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H54" s="5">
         <v>0.5</v>
@@ -23480,7 +23480,7 @@
         <v>16800</v>
       </c>
       <c r="G55" s="5">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="H55" s="5">
         <v>0.5</v>
@@ -23515,7 +23515,7 @@
         <v>16800</v>
       </c>
       <c r="G56" s="5">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="H56" s="5">
         <v>0.5</v>
@@ -23550,7 +23550,7 @@
         <v>29120</v>
       </c>
       <c r="G57" s="5">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="H57" s="5">
         <v>0.5</v>
@@ -23585,7 +23585,7 @@
         <v>2460</v>
       </c>
       <c r="G58" s="5">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="H58" s="5">
         <v>0.5</v>
@@ -23620,7 +23620,7 @@
         <v>2460</v>
       </c>
       <c r="G59" s="5">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="H59" s="5">
         <v>0.5</v>
@@ -23655,7 +23655,7 @@
         <v>2460</v>
       </c>
       <c r="G60" s="5">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="H60" s="5">
         <v>0.5</v>
@@ -23690,7 +23690,7 @@
         <v>3060</v>
       </c>
       <c r="G61" s="5">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="H61" s="5">
         <v>0.5</v>
@@ -23725,7 +23725,7 @@
         <v>3060</v>
       </c>
       <c r="G62" s="5">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="H62" s="5">
         <v>0.5</v>
@@ -23760,7 +23760,7 @@
         <v>5304</v>
       </c>
       <c r="G63" s="5">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="H63" s="5">
         <v>0.5</v>
@@ -23795,7 +23795,7 @@
         <v>20400</v>
       </c>
       <c r="G64" s="5">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="H64" s="5">
         <v>0.5</v>
@@ -23830,7 +23830,7 @@
         <v>20400</v>
       </c>
       <c r="G65" s="5">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="H65" s="5">
         <v>0.5</v>
@@ -23865,7 +23865,7 @@
         <v>20400</v>
       </c>
       <c r="G66" s="5">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="H66" s="5">
         <v>0.5</v>
@@ -23900,7 +23900,7 @@
         <v>120000</v>
       </c>
       <c r="G67" s="5">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="H67" s="5">
         <v>0.5</v>
@@ -23935,7 +23935,7 @@
         <v>120000</v>
       </c>
       <c r="G68" s="5">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="H68" s="5">
         <v>0.5</v>
@@ -23970,7 +23970,7 @@
         <v>208000</v>
       </c>
       <c r="G69" s="5">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="H69" s="5">
         <v>0.5</v>
@@ -24005,7 +24005,7 @@
         <v>5580</v>
       </c>
       <c r="G70" s="5">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="H70" s="5">
         <v>0.5</v>
@@ -24040,7 +24040,7 @@
         <v>5580</v>
       </c>
       <c r="G71" s="5">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="H71" s="5">
         <v>0.5</v>
@@ -24075,7 +24075,7 @@
         <v>5580</v>
       </c>
       <c r="G72" s="5">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="H72" s="5">
         <v>0.5</v>
@@ -24110,7 +24110,7 @@
         <v>6960</v>
       </c>
       <c r="G73" s="5">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="H73" s="5">
         <v>0.5</v>
@@ -24145,7 +24145,7 @@
         <v>6960</v>
       </c>
       <c r="G74" s="5">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="H74" s="5">
         <v>0.5</v>
@@ -24180,7 +24180,7 @@
         <v>12064</v>
       </c>
       <c r="G75" s="5">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="H75" s="5">
         <v>0.5</v>
@@ -24215,7 +24215,7 @@
         <v>150000</v>
       </c>
       <c r="G76" s="5">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="H76" s="5">
         <v>0.5</v>
@@ -24250,7 +24250,7 @@
         <v>150000</v>
       </c>
       <c r="G77" s="5">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="H77" s="5">
         <v>0.5</v>
@@ -24285,7 +24285,7 @@
         <v>150000</v>
       </c>
       <c r="G78" s="5">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="H78" s="5">
         <v>0.5</v>
@@ -24320,7 +24320,7 @@
         <v>570000</v>
       </c>
       <c r="G79" s="5">
-        <v>295</v>
+        <v>133</v>
       </c>
       <c r="H79" s="5">
         <v>0.5</v>
@@ -24355,7 +24355,7 @@
         <v>570000</v>
       </c>
       <c r="G80" s="5">
-        <v>295</v>
+        <v>133</v>
       </c>
       <c r="H80" s="5">
         <v>0.5</v>
@@ -24390,7 +24390,7 @@
         <v>988000</v>
       </c>
       <c r="G81" s="5">
-        <v>472</v>
+        <v>212</v>
       </c>
       <c r="H81" s="5">
         <v>0.5</v>
@@ -24425,7 +24425,7 @@
         <v>12600</v>
       </c>
       <c r="G82" s="5">
-        <v>245</v>
+        <v>110</v>
       </c>
       <c r="H82" s="5">
         <v>0.5</v>
@@ -24460,7 +24460,7 @@
         <v>12600</v>
       </c>
       <c r="G83" s="5">
-        <v>245</v>
+        <v>110</v>
       </c>
       <c r="H83" s="5">
         <v>0.5</v>
@@ -24495,7 +24495,7 @@
         <v>12600</v>
       </c>
       <c r="G84" s="5">
-        <v>245</v>
+        <v>110</v>
       </c>
       <c r="H84" s="5">
         <v>0.5</v>
@@ -24530,7 +24530,7 @@
         <v>15600</v>
       </c>
       <c r="G85" s="5">
-        <v>295</v>
+        <v>133</v>
       </c>
       <c r="H85" s="5">
         <v>0.5</v>
@@ -24565,7 +24565,7 @@
         <v>15600</v>
       </c>
       <c r="G86" s="5">
-        <v>295</v>
+        <v>133</v>
       </c>
       <c r="H86" s="5">
         <v>0.5</v>
@@ -24600,7 +24600,7 @@
         <v>27040</v>
       </c>
       <c r="G87" s="5">
-        <v>472</v>
+        <v>212</v>
       </c>
       <c r="H87" s="5">
         <v>0.5</v>
@@ -35211,7 +35211,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I337"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13.375" customWidth="1"/>
@@ -42373,46 +42373,116 @@
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A334" s="5" t="s">
-        <v>3210</v>
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t>res8000018</t>
+        </is>
       </c>
       <c r="B334" s="5">
-        <v>90</v>
-      </c>
-      <c r="C334" s="4" t="s">
-        <v>3211</v>
-      </c>
-      <c r="D334" s="4" t="s">
-        <v>3212</v>
+        <v>80</v>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>sheet.png</t>
+        </is>
+      </c>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>Fix_Resource/투사체/공격형 건물 투사체/sheet.png</t>
+        </is>
       </c>
       <c r="E334" s="5">
         <v>1</v>
       </c>
       <c r="F334" s="5"/>
-      <c r="G334" s="5"/>
-      <c r="H334" s="5"/>
-      <c r="I334" s="4" t="s">
+      <c r="G334" s="5">
+        <v>16</v>
+      </c>
+      <c r="H334" s="5">
+        <v>24</v>
+      </c>
+      <c r="I334" s="4" t="inlineStr">
+        <is>
+          <t>투사체 · 공격형 건물 공통 (시트 4×4, 프레임 256×128px, 공이 왼쪽·꼬리 오른쪽 = 왼쪽으로 날아가는 그림. 낱장은 frames 폴더)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t>res8000019</t>
+        </is>
+      </c>
+      <c r="B335" s="5">
+        <v>80</v>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>sheet.png</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>Fix_Resource/투사체/공중 유닛 투사체/sheet.png</t>
+        </is>
+      </c>
+      <c r="E335" s="5">
+        <v>1</v>
+      </c>
+      <c r="F335" s="5"/>
+      <c r="G335" s="5">
+        <v>16</v>
+      </c>
+      <c r="H335" s="5">
+        <v>24</v>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>투사체 · 공중 유닛 공통 (시트 4×4, 프레임 256×128px, 공이 왼쪽·꼬리 오른쪽 = 왼쪽으로 날아가는 그림. 낱장은 frames 폴더)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A336" s="5" t="s">
+        <v>3210</v>
+      </c>
+      <c r="B336" s="5">
+        <v>90</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>3211</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>3212</v>
+      </c>
+      <c r="E336" s="5">
+        <v>1</v>
+      </c>
+      <c r="F336" s="5"/>
+      <c r="G336" s="5"/>
+      <c r="H336" s="5"/>
+      <c r="I336" s="4" t="s">
         <v>3213</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A335" s="5" t="s">
+    <row r="337" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A337" s="5" t="s">
         <v>3214</v>
       </c>
-      <c r="B335" s="5">
+      <c r="B337" s="5">
         <v>91</v>
       </c>
-      <c r="C335" s="4" t="s">
+      <c r="C337" s="4" t="s">
         <v>3215</v>
       </c>
-      <c r="D335" s="4" t="s">
+      <c r="D337" s="4" t="s">
         <v>3216</v>
       </c>
-      <c r="E335" s="5"/>
-      <c r="F335" s="5"/>
-      <c r="G335" s="5"/>
-      <c r="H335" s="5"/>
-      <c r="I335" s="4" t="s">
+      <c r="E337" s="5"/>
+      <c r="F337" s="5"/>
+      <c r="G337" s="5"/>
+      <c r="H337" s="5"/>
+      <c r="I337" s="4" t="s">
         <v>3217</v>
       </c>
     </row>
@@ -42424,7 +42494,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.375" customWidth="1"/>
@@ -42851,6 +42921,52 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
         <v>3550</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>projectile_res_building</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>res8000018</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>res_id</t>
+        </is>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>공격형 건물·랜드마크 공통 투사체 리소스 (resource.res_id)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>projectile_res_air_unit</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>res8000019</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>res_id</t>
+        </is>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>공중 유닛 공통 투사체 리소스 (resource.res_id)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -19170,7 +19170,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="5">
-        <v>3780</v>
+        <v>2835</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
@@ -19206,10 +19206,10 @@
         <v>7</v>
       </c>
       <c r="E36" s="5">
-        <v>2130</v>
+        <v>1598</v>
       </c>
       <c r="F36" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36" s="5">
         <v>1</v>
@@ -19242,7 +19242,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="5">
-        <v>6757</v>
+        <v>5068</v>
       </c>
       <c r="F37" s="5">
         <v>2</v>
@@ -19276,7 +19276,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="5">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="F38" s="5">
         <v>0</v>
@@ -19562,7 +19562,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="5">
-        <v>1440</v>
+        <v>864</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
@@ -19598,10 +19598,10 @@
         <v>7</v>
       </c>
       <c r="E47" s="5">
-        <v>749</v>
+        <v>449</v>
       </c>
       <c r="F47" s="5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G47" s="5">
         <v>1</v>
@@ -19634,7 +19634,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="5">
-        <v>2400</v>
+        <v>1440</v>
       </c>
       <c r="F48" s="5">
         <v>0</v>
@@ -19670,7 +19670,7 @@
         <v>24</v>
       </c>
       <c r="E49" s="5">
-        <v>9800</v>
+        <v>5880</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
@@ -19706,10 +19706,10 @@
         <v>9</v>
       </c>
       <c r="E50" s="5">
-        <v>6625</v>
+        <v>3975</v>
       </c>
       <c r="F50" s="5">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="G50" s="5">
         <v>1</v>
@@ -19742,10 +19742,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>57330</v>
+        <v>28665</v>
       </c>
       <c r="F51" s="5">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G51" s="5">
         <v>1</v>
@@ -19776,7 +19776,7 @@
         <v>17</v>
       </c>
       <c r="E52" s="5">
-        <v>14700</v>
+        <v>8820</v>
       </c>
       <c r="F52" s="5">
         <v>0</v>
@@ -20062,7 +20062,7 @@
         <v>25</v>
       </c>
       <c r="E60" s="5">
-        <v>10800</v>
+        <v>6480</v>
       </c>
       <c r="F60" s="5">
         <v>0</v>
@@ -20098,10 +20098,10 @@
         <v>9</v>
       </c>
       <c r="E61" s="5">
-        <v>5616</v>
+        <v>3370</v>
       </c>
       <c r="F61" s="5">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G61" s="5">
         <v>1</v>
@@ -20134,7 +20134,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="5">
-        <v>18000</v>
+        <v>10800</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
@@ -20170,7 +20170,7 @@
         <v>28</v>
       </c>
       <c r="E63" s="5">
-        <v>212800</v>
+        <v>53200</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
@@ -20206,10 +20206,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="5">
-        <v>143853</v>
+        <v>35963</v>
       </c>
       <c r="F64" s="5">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="G64" s="5">
         <v>1</v>
@@ -20242,10 +20242,10 @@
         <v>1</v>
       </c>
       <c r="E65" s="5">
-        <v>414960</v>
+        <v>103740</v>
       </c>
       <c r="F65" s="5">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G65" s="5">
         <v>1</v>
@@ -20276,7 +20276,7 @@
         <v>19</v>
       </c>
       <c r="E66" s="5">
-        <v>42000</v>
+        <v>10500</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
@@ -20562,7 +20562,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="5">
-        <v>30600</v>
+        <v>16830</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
@@ -20598,10 +20598,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="5">
-        <v>15912</v>
+        <v>8752</v>
       </c>
       <c r="F75" s="5">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="G75" s="5">
         <v>1</v>
@@ -20634,7 +20634,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="5">
-        <v>51000</v>
+        <v>28050</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
@@ -20670,7 +20670,7 @@
         <v>32</v>
       </c>
       <c r="E77" s="5">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F77" s="5">
         <v>0</v>
@@ -20706,10 +20706,10 @@
         <v>13</v>
       </c>
       <c r="E78" s="5">
-        <v>135200</v>
+        <v>67600</v>
       </c>
       <c r="F78" s="5">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="G78" s="5">
         <v>1</v>
@@ -20742,7 +20742,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="5">
-        <v>1170000</v>
+        <v>585000</v>
       </c>
       <c r="F79" s="5">
         <v>180</v>
@@ -20776,7 +20776,7 @@
         <v>21</v>
       </c>
       <c r="E80" s="5">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="F80" s="5">
         <v>0</v>
@@ -21062,7 +21062,7 @@
         <v>33</v>
       </c>
       <c r="E88" s="5">
-        <v>225000</v>
+        <v>112500</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -21098,10 +21098,10 @@
         <v>13</v>
       </c>
       <c r="E89" s="5">
-        <v>117000</v>
+        <v>58500</v>
       </c>
       <c r="F89" s="5">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="G89" s="5">
         <v>1</v>
@@ -21134,7 +21134,7 @@
         <v>22</v>
       </c>
       <c r="E90" s="5">
-        <v>375000</v>
+        <v>187500</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
@@ -21170,7 +21170,7 @@
         <v>36</v>
       </c>
       <c r="E91" s="5">
-        <v>950000</v>
+        <v>266000</v>
       </c>
       <c r="F91" s="5">
         <v>0</v>
@@ -21206,10 +21206,10 @@
         <v>15</v>
       </c>
       <c r="E92" s="5">
-        <v>642200</v>
+        <v>179816</v>
       </c>
       <c r="F92" s="5">
-        <v>399</v>
+        <v>519</v>
       </c>
       <c r="G92" s="5">
         <v>1</v>
@@ -21242,10 +21242,10 @@
         <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>2778750</v>
+        <v>778050</v>
       </c>
       <c r="F93" s="5">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="G93" s="5">
         <v>1</v>
@@ -21276,7 +21276,7 @@
         <v>23</v>
       </c>
       <c r="E94" s="5">
-        <v>1425000</v>
+        <v>399000</v>
       </c>
       <c r="F94" s="5">
         <v>0</v>
@@ -23480,7 +23480,7 @@
         <v>16800</v>
       </c>
       <c r="G55" s="5">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H55" s="5">
         <v>0.5</v>
@@ -23515,7 +23515,7 @@
         <v>16800</v>
       </c>
       <c r="G56" s="5">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H56" s="5">
         <v>0.5</v>
@@ -23550,7 +23550,7 @@
         <v>29120</v>
       </c>
       <c r="G57" s="5">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H57" s="5">
         <v>0.5</v>
@@ -24320,7 +24320,7 @@
         <v>570000</v>
       </c>
       <c r="G79" s="5">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="H79" s="5">
         <v>0.5</v>
@@ -24355,7 +24355,7 @@
         <v>570000</v>
       </c>
       <c r="G80" s="5">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="H80" s="5">
         <v>0.5</v>
@@ -24390,7 +24390,7 @@
         <v>988000</v>
       </c>
       <c r="G81" s="5">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="H81" s="5">
         <v>0.5</v>

--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -29371,7 +29371,7 @@
       </c>
       <c r="I4" s="51"/>
       <c r="J4" s="51">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K4" s="51">
         <v>1</v>
@@ -29693,15 +29693,15 @@
       </c>
       <c r="F11" s="56"/>
       <c r="G11" s="51">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H11" s="51">
         <v>45</v>
       </c>
-      <c r="I11" s="51">
-        <v>33</v>
-      </c>
-      <c r="J11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51">
+        <v>1.35</v>
+      </c>
       <c r="K11" s="51">
         <v>8</v>
       </c>
@@ -29894,7 +29894,7 @@
         <v>25</v>
       </c>
       <c r="H15" s="51">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I15" s="51">
         <v>33</v>
@@ -30288,7 +30288,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="51">
-        <v>90000</v>
+        <v>72000</v>
       </c>
       <c r="I23" s="51"/>
       <c r="J23" s="51">
@@ -30578,7 +30578,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="51">
-        <v>18000</v>
+        <v>14400</v>
       </c>
       <c r="I29" s="51"/>
       <c r="J29" s="51">
@@ -30671,23 +30671,23 @@
         <v>1472</v>
       </c>
       <c r="G31" s="51">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H31" s="51">
-        <v>3000000</v>
-      </c>
-      <c r="I31" s="51">
-        <v>2400000</v>
-      </c>
-      <c r="J31" s="51"/>
+        <v>20000</v>
+      </c>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51">
+        <v>1.25</v>
+      </c>
       <c r="K31" s="51">
         <v>32</v>
       </c>
       <c r="L31" s="51">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M31" s="51">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="N31" s="51">
         <v>2</v>

--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -24706,7 +24706,7 @@
         <v>1283</v>
       </c>
       <c r="E4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>1284</v>
@@ -24726,7 +24726,7 @@
         <v>1287</v>
       </c>
       <c r="E5" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>1288</v>
@@ -24746,7 +24746,7 @@
         <v>1291</v>
       </c>
       <c r="E6" s="5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>1292</v>
@@ -24766,7 +24766,7 @@
         <v>1295</v>
       </c>
       <c r="E7" s="5">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>1296</v>
@@ -24786,7 +24786,7 @@
         <v>1299</v>
       </c>
       <c r="E8" s="5">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>1300</v>
@@ -24806,7 +24806,7 @@
         <v>1303</v>
       </c>
       <c r="E9" s="5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>1304</v>

--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -19170,7 +19170,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="5">
-        <v>2835</v>
+        <v>1400</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
@@ -19206,7 +19206,7 @@
         <v>7</v>
       </c>
       <c r="E36" s="5">
-        <v>1598</v>
+        <v>800</v>
       </c>
       <c r="F36" s="5">
         <v>8</v>
@@ -19562,7 +19562,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="5">
-        <v>864</v>
+        <v>1150</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
@@ -19598,7 +19598,7 @@
         <v>7</v>
       </c>
       <c r="E47" s="5">
-        <v>449</v>
+        <v>600</v>
       </c>
       <c r="F47" s="5">
         <v>23</v>
@@ -19634,7 +19634,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="5">
-        <v>1440</v>
+        <v>1900</v>
       </c>
       <c r="F48" s="5">
         <v>0</v>
@@ -19670,7 +19670,7 @@
         <v>24</v>
       </c>
       <c r="E49" s="5">
-        <v>5880</v>
+        <v>2270</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
@@ -19706,7 +19706,7 @@
         <v>9</v>
       </c>
       <c r="E50" s="5">
-        <v>3975</v>
+        <v>1530</v>
       </c>
       <c r="F50" s="5">
         <v>140</v>
@@ -19742,7 +19742,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>28665</v>
+        <v>11100</v>
       </c>
       <c r="F51" s="5">
         <v>58</v>
@@ -19776,7 +19776,7 @@
         <v>17</v>
       </c>
       <c r="E52" s="5">
-        <v>8820</v>
+        <v>3400</v>
       </c>
       <c r="F52" s="5">
         <v>0</v>
@@ -20062,7 +20062,7 @@
         <v>25</v>
       </c>
       <c r="E60" s="5">
-        <v>6480</v>
+        <v>5370</v>
       </c>
       <c r="F60" s="5">
         <v>0</v>
@@ -20098,7 +20098,7 @@
         <v>9</v>
       </c>
       <c r="E61" s="5">
-        <v>3370</v>
+        <v>2790</v>
       </c>
       <c r="F61" s="5">
         <v>47</v>
@@ -20134,7 +20134,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="5">
-        <v>10800</v>
+        <v>8940</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
@@ -20170,7 +20170,7 @@
         <v>28</v>
       </c>
       <c r="E63" s="5">
-        <v>53200</v>
+        <v>18200</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>11</v>
       </c>
       <c r="E64" s="5">
-        <v>35963</v>
+        <v>12300</v>
       </c>
       <c r="F64" s="5">
         <v>112</v>
@@ -20242,7 +20242,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="5">
-        <v>103740</v>
+        <v>35500</v>
       </c>
       <c r="F65" s="5">
         <v>34</v>
@@ -20276,7 +20276,7 @@
         <v>19</v>
       </c>
       <c r="E66" s="5">
-        <v>10500</v>
+        <v>3590</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
@@ -20562,7 +20562,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="5">
-        <v>16830</v>
+        <v>25700</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
@@ -20598,7 +20598,7 @@
         <v>11</v>
       </c>
       <c r="E75" s="5">
-        <v>8752</v>
+        <v>13300</v>
       </c>
       <c r="F75" s="5">
         <v>96</v>
@@ -20634,7 +20634,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="5">
-        <v>28050</v>
+        <v>42800</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
@@ -20670,7 +20670,7 @@
         <v>32</v>
       </c>
       <c r="E77" s="5">
-        <v>100000</v>
+        <v>52200</v>
       </c>
       <c r="F77" s="5">
         <v>0</v>
@@ -20706,7 +20706,7 @@
         <v>13</v>
       </c>
       <c r="E78" s="5">
-        <v>67600</v>
+        <v>35300</v>
       </c>
       <c r="F78" s="5">
         <v>192</v>
@@ -20742,7 +20742,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="5">
-        <v>585000</v>
+        <v>305000</v>
       </c>
       <c r="F79" s="5">
         <v>180</v>
@@ -20776,7 +20776,7 @@
         <v>21</v>
       </c>
       <c r="E80" s="5">
-        <v>150000</v>
+        <v>78300</v>
       </c>
       <c r="F80" s="5">
         <v>0</v>
@@ -21062,7 +21062,7 @@
         <v>33</v>
       </c>
       <c r="E88" s="5">
-        <v>112500</v>
+        <v>125000</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -21098,7 +21098,7 @@
         <v>13</v>
       </c>
       <c r="E89" s="5">
-        <v>58500</v>
+        <v>64800</v>
       </c>
       <c r="F89" s="5">
         <v>199</v>
@@ -21134,7 +21134,7 @@
         <v>22</v>
       </c>
       <c r="E90" s="5">
-        <v>187500</v>
+        <v>208000</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
@@ -23057,7 +23057,7 @@
         <v>1178</v>
       </c>
       <c r="F43" s="5">
-        <v>5880</v>
+        <v>2270</v>
       </c>
       <c r="G43" s="5">
         <v>15</v>
@@ -23092,7 +23092,7 @@
         <v>1178</v>
       </c>
       <c r="F44" s="5">
-        <v>5880</v>
+        <v>2270</v>
       </c>
       <c r="G44" s="5">
         <v>15</v>
@@ -23127,7 +23127,7 @@
         <v>1187</v>
       </c>
       <c r="F45" s="5">
-        <v>10192</v>
+        <v>3930</v>
       </c>
       <c r="G45" s="5">
         <v>24</v>
@@ -23372,7 +23372,7 @@
         <v>1204</v>
       </c>
       <c r="F52" s="5">
-        <v>7200</v>
+        <v>5960</v>
       </c>
       <c r="G52" s="5">
         <v>18</v>
@@ -23407,7 +23407,7 @@
         <v>1204</v>
       </c>
       <c r="F53" s="5">
-        <v>7200</v>
+        <v>5960</v>
       </c>
       <c r="G53" s="5">
         <v>18</v>
@@ -23442,7 +23442,7 @@
         <v>1204</v>
       </c>
       <c r="F54" s="5">
-        <v>7200</v>
+        <v>5960</v>
       </c>
       <c r="G54" s="5">
         <v>18</v>
@@ -23477,7 +23477,7 @@
         <v>1204</v>
       </c>
       <c r="F55" s="5">
-        <v>16800</v>
+        <v>5740</v>
       </c>
       <c r="G55" s="5">
         <v>46</v>
@@ -23512,7 +23512,7 @@
         <v>1204</v>
       </c>
       <c r="F56" s="5">
-        <v>16800</v>
+        <v>5740</v>
       </c>
       <c r="G56" s="5">
         <v>46</v>
@@ -23547,7 +23547,7 @@
         <v>1213</v>
       </c>
       <c r="F57" s="5">
-        <v>29120</v>
+        <v>9950</v>
       </c>
       <c r="G57" s="5">
         <v>75</v>
@@ -23792,7 +23792,7 @@
         <v>1230</v>
       </c>
       <c r="F64" s="5">
-        <v>20400</v>
+        <v>31100</v>
       </c>
       <c r="G64" s="5">
         <v>37</v>
@@ -23827,7 +23827,7 @@
         <v>1230</v>
       </c>
       <c r="F65" s="5">
-        <v>20400</v>
+        <v>31100</v>
       </c>
       <c r="G65" s="5">
         <v>37</v>
@@ -23862,7 +23862,7 @@
         <v>1230</v>
       </c>
       <c r="F66" s="5">
-        <v>20400</v>
+        <v>31100</v>
       </c>
       <c r="G66" s="5">
         <v>37</v>
@@ -23897,7 +23897,7 @@
         <v>1230</v>
       </c>
       <c r="F67" s="5">
-        <v>120000</v>
+        <v>62600</v>
       </c>
       <c r="G67" s="5">
         <v>64</v>
@@ -23932,7 +23932,7 @@
         <v>1230</v>
       </c>
       <c r="F68" s="5">
-        <v>120000</v>
+        <v>62600</v>
       </c>
       <c r="G68" s="5">
         <v>64</v>
@@ -23967,7 +23967,7 @@
         <v>1239</v>
       </c>
       <c r="F69" s="5">
-        <v>208000</v>
+        <v>109000</v>
       </c>
       <c r="G69" s="5">
         <v>103</v>
@@ -24212,7 +24212,7 @@
         <v>1256</v>
       </c>
       <c r="F76" s="5">
-        <v>150000</v>
+        <v>166000</v>
       </c>
       <c r="G76" s="5">
         <v>76</v>
@@ -24247,7 +24247,7 @@
         <v>1256</v>
       </c>
       <c r="F77" s="5">
-        <v>150000</v>
+        <v>166000</v>
       </c>
       <c r="G77" s="5">
         <v>76</v>
@@ -24282,7 +24282,7 @@
         <v>1256</v>
       </c>
       <c r="F78" s="5">
-        <v>150000</v>
+        <v>166000</v>
       </c>
       <c r="G78" s="5">
         <v>76</v>
@@ -30288,7 +30288,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="51">
-        <v>72000</v>
+        <v>14400</v>
       </c>
       <c r="I23" s="51"/>
       <c r="J23" s="51">

--- a/Docs/20261012_데이터테이블_Ver02.xlsx
+++ b/Docs/20261012_데이터테이블_Ver02.xlsx
@@ -20170,7 +20170,7 @@
         <v>28</v>
       </c>
       <c r="E63" s="5">
-        <v>18200</v>
+        <v>62200</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
@@ -20206,10 +20206,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="5">
-        <v>12300</v>
+        <v>42000</v>
       </c>
       <c r="F64" s="5">
-        <v>112</v>
+        <v>392</v>
       </c>
       <c r="G64" s="5">
         <v>1</v>
@@ -20242,10 +20242,10 @@
         <v>1</v>
       </c>
       <c r="E65" s="5">
-        <v>35500</v>
+        <v>122000</v>
       </c>
       <c r="F65" s="5">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="G65" s="5">
         <v>1</v>
@@ -20276,7 +20276,7 @@
         <v>19</v>
       </c>
       <c r="E66" s="5">
-        <v>3590</v>
+        <v>12300</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
@@ -20562,7 +20562,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="5">
-        <v>25700</v>
+        <v>41400</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
@@ -20598,10 +20598,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="5">
-        <v>13300</v>
+        <v>21400</v>
       </c>
       <c r="F75" s="5">
-        <v>96</v>
+        <v>513</v>
       </c>
       <c r="G75" s="5">
         <v>1</v>
@@ -20634,7 +20634,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="5">
-        <v>42800</v>
+        <v>69000</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
@@ -20670,7 +20670,7 @@
         <v>32</v>
       </c>
       <c r="E77" s="5">
-        <v>52200</v>
+        <v>71700</v>
       </c>
       <c r="F77" s="5">
         <v>0</v>
@@ -20706,7 +20706,7 @@
         <v>13</v>
       </c>
       <c r="E78" s="5">
-        <v>35300</v>
+        <v>48500</v>
       </c>
       <c r="F78" s="5">
         <v>192</v>
@@ -20742,7 +20742,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="5">
-        <v>305000</v>
+        <v>419000</v>
       </c>
       <c r="F79" s="5">
         <v>180</v>
@@ -20776,7 +20776,7 @@
         <v>21</v>
       </c>
       <c r="E80" s="5">
-        <v>78300</v>
+        <v>108000</v>
       </c>
       <c r="F80" s="5">
         <v>0</v>
@@ -21062,7 +21062,7 @@
         <v>33</v>
       </c>
       <c r="E88" s="5">
-        <v>125000</v>
+        <v>146000</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -21098,7 +21098,7 @@
         <v>13</v>
       </c>
       <c r="E89" s="5">
-        <v>64800</v>
+        <v>75800</v>
       </c>
       <c r="F89" s="5">
         <v>199</v>
@@ -21134,7 +21134,7 @@
         <v>22</v>
       </c>
       <c r="E90" s="5">
-        <v>208000</v>
+        <v>243000</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
@@ -23477,10 +23477,10 @@
         <v>1204</v>
       </c>
       <c r="F55" s="5">
-        <v>5740</v>
+        <v>19600</v>
       </c>
       <c r="G55" s="5">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="H55" s="5">
         <v>0.5</v>
@@ -23512,10 +23512,10 @@
         <v>1204</v>
       </c>
       <c r="F56" s="5">
-        <v>5740</v>
+        <v>19600</v>
       </c>
       <c r="G56" s="5">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="H56" s="5">
         <v>0.5</v>
@@ -23547,10 +23547,10 @@
         <v>1213</v>
       </c>
       <c r="F57" s="5">
-        <v>9950</v>
+        <v>34000</v>
       </c>
       <c r="G57" s="5">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="H57" s="5">
         <v>0.5</v>
@@ -23792,10 +23792,10 @@
         <v>1230</v>
       </c>
       <c r="F64" s="5">
-        <v>31100</v>
+        <v>50100</v>
       </c>
       <c r="G64" s="5">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="H64" s="5">
         <v>0.5</v>
@@ -23827,10 +23827,10 @@
         <v>1230</v>
       </c>
       <c r="F65" s="5">
-        <v>31100</v>
+        <v>50100</v>
       </c>
       <c r="G65" s="5">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="H65" s="5">
         <v>0.5</v>
@@ -23862,10 +23862,10 @@
         <v>1230</v>
       </c>
       <c r="F66" s="5">
-        <v>31100</v>
+        <v>50100</v>
       </c>
       <c r="G66" s="5">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="H66" s="5">
         <v>0.5</v>
@@ -23897,7 +23897,7 @@
         <v>1230</v>
       </c>
       <c r="F67" s="5">
-        <v>62600</v>
+        <v>86000</v>
       </c>
       <c r="G67" s="5">
         <v>64</v>
@@ -23932,7 +23932,7 @@
         <v>1230</v>
       </c>
       <c r="F68" s="5">
-        <v>62600</v>
+        <v>86000</v>
       </c>
       <c r="G68" s="5">
         <v>64</v>
@@ -23967,7 +23967,7 @@
         <v>1239</v>
       </c>
       <c r="F69" s="5">
-        <v>109000</v>
+        <v>150000</v>
       </c>
       <c r="G69" s="5">
         <v>103</v>
@@ -24212,7 +24212,7 @@
         <v>1256</v>
       </c>
       <c r="F76" s="5">
-        <v>166000</v>
+        <v>194000</v>
       </c>
       <c r="G76" s="5">
         <v>76</v>
@@ -24247,7 +24247,7 @@
         <v>1256</v>
       </c>
       <c r="F77" s="5">
-        <v>166000</v>
+        <v>194000</v>
       </c>
       <c r="G77" s="5">
         <v>76</v>
@@ -24282,7 +24282,7 @@
         <v>1256</v>
       </c>
       <c r="F78" s="5">
-        <v>166000</v>
+        <v>194000</v>
       </c>
       <c r="G78" s="5">
         <v>76</v>
@@ -30335,10 +30335,10 @@
         <v>4</v>
       </c>
       <c r="H24" s="51">
-        <v>270000</v>
+        <v>90000</v>
       </c>
       <c r="I24" s="51">
-        <v>405000</v>
+        <v>126000</v>
       </c>
       <c r="J24" s="51"/>
       <c r="K24" s="51">
